--- a/Dokumentace/Nefunkcni_pozadavky_tankovani.xlsx
+++ b/Dokumentace/Nefunkcni_pozadavky_tankovani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jirivavra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12FA73BD-898F-5E45-B3BC-E33E62FA6EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24A2DFF-3916-6246-84B3-D17EBF3FB799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Nefunkční požadavky" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -203,7 +202,7 @@
     <t>Kompatibilita se systémem Android</t>
   </si>
   <si>
-    <t>Aplikace musí být plně funkční a vizuálně responzivní na mobilních zařízeních s operačním systémem Android 8.0 (API level 26) a novějším.</t>
+    <t>Aplikace musí být plně funkční a vizuálně responzivní na mobilních zařízeních s operačním systémem Android 9.0 (API level 28) a novějším.</t>
   </si>
 </sst>
 </file>

--- a/Dokumentace/Nefunkcni_pozadavky_tankovani.xlsx
+++ b/Dokumentace/Nefunkcni_pozadavky_tankovani.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jirivavra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24A2DFF-3916-6246-84B3-D17EBF3FB799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A9E0C77-74F3-1442-9A7E-7D7E530BF8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nefunkční požadavky" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -46,7 +47,7 @@
     <t>Rychlost rozpoznání údajů</t>
   </si>
   <si>
-    <t>Doba od pořízení fotografie displeje stojanu nebo tachometru po zobrazení předvyplněných hodnot ve formuláři nesmí na referenčním zařízení překročit 2,5 sekundy v 95 % případů.</t>
+    <t>Doba od pořízení fotografie displeje stojanu po zobrazení předvyplněných hodnot ve formuláři nesmí na referenčním zařízení překročit 2,5 sekundy v 95 % případů.</t>
   </si>
   <si>
     <t>NFP-02</t>
@@ -94,7 +95,7 @@
     <t>Rychlost vykreslení grafů</t>
   </si>
   <si>
-    <t>Vygenerování a zobrazení grafů měsíční spotřeby, výdajů a ujetých kilometrů nesmí trvat déle než 500 ms od přechodu na obrazovku statistik.</t>
+    <t>Vygenerování a zobrazení grafů měsíční spotřeby a výdajů nesmí trvat déle než 500 ms od přechodu na obrazovku statistik.</t>
   </si>
   <si>
     <t>NFP-07</t>
@@ -115,7 +116,7 @@
     <t>Numerická přesnost údajů</t>
   </si>
   <si>
-    <t>Množství paliva, jednotková cena, celková cena a průměrná spotřeba (l/100 km) musí být ukládány a zobrazovány s přesností na 2 desetinná místa se standardním matematickým zaokrouhlením. Stav tachometru se eviduje v celých kilometrech.</t>
+    <t>Množství paliva, jednotková cena a celková cena musí být ukládány a zobrazovány s přesností na 2 desetinná místa se standardním matematickým zaokrouhlením. Stav tachometru se eviduje v celých kilometrech.</t>
   </si>
   <si>
     <t>NFP-09</t>
@@ -145,7 +146,7 @@
     <t>Plná dostupnost v offline režimu</t>
   </si>
   <si>
-    <t>100 % funkcí pro evidenci vozidel, zadávání tankování, lokální OCR rozpoznávání z fotografie, výpočet statistik a zobrazení grafů musí fungovat plně offline bez připojení k internetu.</t>
+    <t>100 % funkcí pro evidenci vozidel, zadávání tankování, lokální OCR rozpoznávání z fotografie, zobrazení historie i statistik musí fungovat plně offline bez připojení k internetu.</t>
   </si>
   <si>
     <t>NFP-12</t>
@@ -278,12 +279,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF7F8FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F8FB"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -608,35 +609,35 @@
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="1:3" ht="59" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="59" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="73" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="12" t="s">
         <v>14</v>
       </c>
     </row>
@@ -648,46 +649,46 @@
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" ht="46" customHeight="1">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="59" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="59" customHeight="1">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:3" ht="46" customHeight="1">
+      <c r="A13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="59" customHeight="1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>27</v>
       </c>
     </row>
@@ -698,36 +699,36 @@
       </c>
       <c r="C15" s="5"/>
     </row>
-    <row r="16" spans="1:3" ht="73" customHeight="1">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:3" ht="59" customHeight="1">
+      <c r="A16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="73" customHeight="1">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="73" customHeight="1">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -739,35 +740,35 @@
       <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3" ht="59" customHeight="1">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="59" customHeight="1">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="73" customHeight="1">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="9" t="s">
         <v>47</v>
       </c>
     </row>
@@ -779,46 +780,46 @@
       <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:3" ht="59" customHeight="1">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="73" customHeight="1">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="59" customHeight="1">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="59" customHeight="1">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="12" t="s">
         <v>60</v>
       </c>
     </row>
@@ -833,14 +834,14 @@
       <c r="C29" s="13"/>
     </row>
     <row r="30" spans="1:3" ht="59" customHeight="1"/>
-    <row r="31" spans="1:3" ht="91" customHeight="1"/>
+    <row r="31" spans="1:3" ht="59" customHeight="1"/>
     <row r="32" spans="1:3" ht="59" customHeight="1"/>
-    <row r="33" ht="59" customHeight="1"/>
-    <row r="34" ht="27" customHeight="1"/>
+    <row r="33" ht="27" customHeight="1"/>
+    <row r="34" ht="59" customHeight="1"/>
     <row r="35" ht="59" customHeight="1"/>
     <row r="36" ht="59" customHeight="1"/>
-    <row r="37" ht="59" customHeight="1"/>
-    <row r="38" ht="46" customHeight="1"/>
+    <row r="37" ht="46" customHeight="1"/>
+    <row r="38" ht="15" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Dokumentace/Nefunkcni_pozadavky_tankovani.xlsx
+++ b/Dokumentace/Nefunkcni_pozadavky_tankovani.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jirivavra/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Fueling_Management_Tool\Dokumentace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A9E0C77-74F3-1442-9A7E-7D7E530BF8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8903284-0BB7-4E6C-8654-1EC6A1FA9D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="32220" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nefunkční požadavky" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -203,7 +202,7 @@
     <t>Kompatibilita se systémem Android</t>
   </si>
   <si>
-    <t>Aplikace musí být plně funkční a vizuálně responzivní na mobilních zařízeních s operačním systémem Android 9.0 (API level 28) a novějším.</t>
+    <t>Aplikace musí být plně funkční a vizuálně responzivní na mobilních zařízeních s operačním systémem Android 10.0 (API level 29) a novějším.</t>
   </si>
 </sst>
 </file>
@@ -559,7 +558,7 @@
     <tabColor rgb="FF654D9B"/>
   </sheetPr>
   <dimension ref="A1:C38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
